--- a/ใบเบิก177 Update.xlsx
+++ b/ใบเบิก177 Update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47843DD-3B54-47F9-9C22-F80F671AFBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B70C95-5451-4845-9E50-A7C49508B1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="แบบฟอร์มใบเบิก" sheetId="1" r:id="rId1"/>
@@ -497,33 +497,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -827,6 +827,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -840,7 +843,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="22"/>
@@ -852,7 +855,7 @@
       <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="22"/>
@@ -864,7 +867,7 @@
       <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="25" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="22"/>
@@ -876,19 +879,19 @@
       <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
     </row>
     <row r="5" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="28" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -897,20 +900,20 @@
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="32"/>
+      <c r="F5" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="27" t="s">
+      <c r="G5" s="32"/>
+      <c r="H5" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
@@ -929,9 +932,9 @@
       <c r="G6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="30"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="29"/>
+    </row>
+    <row r="7" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -949,7 +952,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -963,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -977,7 +980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -991,7 +994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -1005,7 +1008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -1019,7 +1022,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>7</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>8</v>
       </c>
@@ -1047,7 +1050,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>9</v>
       </c>
@@ -1061,7 +1064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>10</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>11</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>12</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>13</v>
       </c>
@@ -1117,7 +1120,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>14</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>15</v>
       </c>
@@ -1145,7 +1148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>16</v>
       </c>
@@ -1157,7 +1160,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>17</v>
       </c>
@@ -1169,7 +1172,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>18</v>
       </c>
@@ -1181,7 +1184,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>19</v>
       </c>
@@ -1193,7 +1196,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>20</v>
       </c>
@@ -1205,7 +1208,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>21</v>
       </c>
@@ -1217,7 +1220,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>22</v>
       </c>
@@ -1229,7 +1232,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>23</v>
       </c>
@@ -1241,7 +1244,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>24</v>
       </c>
@@ -1253,7 +1256,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>25</v>
       </c>
@@ -1265,7 +1268,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>26</v>
       </c>
@@ -1279,7 +1282,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>27</v>
       </c>
@@ -1293,7 +1296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>28</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>29</v>
       </c>
@@ -1321,7 +1324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>30</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>31</v>
       </c>
@@ -1350,21 +1353,27 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34"/>
+      <c r="A38" s="30"/>
       <c r="B38" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="31">
         <f>SUM(C7:C37)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="24">
+      <c r="D38" s="31">
+        <f>D37</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="31">
+        <f>E37</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="23">
         <f>SUM(F7:F37)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="23">
         <f>SUM(G7:G37)</f>
         <v>0</v>
       </c>
@@ -1373,16 +1382,16 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="25"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="14" t="str">
         <f>"(เงิน"&amp;BAHTTEXT(F38)&amp;")"</f>
         <v>(เงินศูนย์บาทถ้วน)</v>
       </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
       <c r="H39" s="13" t="s">
         <v>47</v>
       </c>
@@ -1392,7 +1401,7 @@
       <c r="B40" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="34" t="s">
         <v>27</v>
       </c>
       <c r="D40" s="22"/>
@@ -1485,6 +1494,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="C46:G46"/>
     <mergeCell ref="F38:F39"/>
     <mergeCell ref="A2:H2"/>
@@ -1495,17 +1513,8 @@
     <mergeCell ref="D38:D39"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="C45:G45"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>